--- a/exports/BOSCHLTD_full_report.xlsx
+++ b/exports/BOSCHLTD_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q62"/>
+  <dimension ref="A1:U62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,22 +557,22 @@
         <v>5.2</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44580.55208333334</v>
+        <v>44581.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>17020</v>
+        <v>16671.05</v>
       </c>
       <c r="I2" t="n">
         <v>16961.60154179536</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K2" t="n">
-        <v>-1.94</v>
+        <v>-3.95</v>
       </c>
       <c r="L2" t="n">
-        <v>2.46</v>
+        <v>3.95</v>
       </c>
       <c r="M2" t="n">
         <v>0.37</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>6.93</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44652.55208333334</v>
+        <v>44655.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>14575.9</v>
+        <v>14766.3</v>
       </c>
       <c r="I3" t="n">
         <v>14653.32142695817</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>71.16666666666667</v>
+        <v>74</v>
       </c>
       <c r="K3" t="n">
-        <v>12.57</v>
+        <v>11.43</v>
       </c>
       <c r="L3" t="n">
         <v>2.73</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>98</v>
+        <v>99</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>4</v>
+      </c>
+      <c r="U3" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -648,22 +695,22 @@
         <v>4.5</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44664.55208333334</v>
+        <v>44669.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>14555</v>
+        <v>14438.3</v>
       </c>
       <c r="I4" t="n">
         <v>14492.33822984348</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>14</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.43</v>
+        <v>-2.22</v>
       </c>
       <c r="L4" t="n">
-        <v>2.05</v>
+        <v>3.16</v>
       </c>
       <c r="M4" t="n">
         <v>0.28</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>4.2</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44698.55208333334</v>
+        <v>44699.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>13612</v>
+        <v>14100</v>
       </c>
       <c r="I5" t="n">
         <v>13902.3067306667</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>30</v>
       </c>
       <c r="K5" t="n">
-        <v>5.72</v>
+        <v>2.34</v>
       </c>
       <c r="L5" t="n">
         <v>2.44</v>
@@ -726,7 +785,7 @@
         <v>1.84</v>
       </c>
       <c r="N5" t="n">
-        <v>2.82</v>
+        <v>3.95</v>
       </c>
       <c r="O5" t="n">
         <v>0.17</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>7.8</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44722.55208333334</v>
+        <v>44725.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>14161.05</v>
+        <v>13911.1</v>
       </c>
       <c r="I6" t="n">
         <v>14010.75641706796</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>23.16666666666667</v>
+        <v>26</v>
       </c>
       <c r="K6" t="n">
-        <v>0.43</v>
+        <v>-1.34</v>
       </c>
       <c r="L6" t="n">
         <v>6.53</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>5.65</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44735.55208333334</v>
+        <v>44736.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>13822.25</v>
+        <v>13957.5</v>
       </c>
       <c r="I7" t="n">
         <v>13917.84429758047</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K7" t="n">
-        <v>0.64</v>
+        <v>-0.33</v>
       </c>
       <c r="L7" t="n">
         <v>1.68</v>
@@ -840,7 +923,7 @@
         <v>1.5</v>
       </c>
       <c r="N7" t="n">
-        <v>2.56</v>
+        <v>3.46</v>
       </c>
       <c r="O7" t="n">
         <v>-1.91</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>4.91</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44820.38541666666</v>
+        <v>44820.55208333334</v>
       </c>
       <c r="H8" t="n">
-        <v>17052.05</v>
+        <v>16893</v>
       </c>
       <c r="I8" t="n">
         <v>17028.78347880619</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>84</v>
+        <v>84.16666666666667</v>
       </c>
       <c r="K8" t="n">
-        <v>22.17</v>
+        <v>21.03</v>
       </c>
       <c r="L8" t="n">
         <v>0.41</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>115</v>
+        <v>116</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>4</v>
+      </c>
+      <c r="U8" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>4.68</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44862.55208333334</v>
+        <v>44865.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>16100</v>
+        <v>16494</v>
       </c>
       <c r="I9" t="n">
         <v>16130.81745560509</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>42</v>
+        <v>44.83333333333334</v>
       </c>
       <c r="K9" t="n">
-        <v>4.69</v>
+        <v>2.36</v>
       </c>
       <c r="L9" t="n">
         <v>2.11</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>4.82</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44886.38541666666</v>
+        <v>44886.55208333334</v>
       </c>
       <c r="H10" t="n">
-        <v>16441.9</v>
+        <v>16346.75</v>
       </c>
       <c r="I10" t="n">
         <v>16366.73300369736</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>21</v>
+        <v>21.16666666666667</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.32</v>
+        <v>-0.89</v>
       </c>
       <c r="L10" t="n">
         <v>2.34</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1047,22 +1178,22 @@
         <v>4.39</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44896.55208333334</v>
+        <v>44897.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>17025.05</v>
+        <v>17150.1</v>
       </c>
       <c r="I11" t="n">
         <v>17051.30767763234</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>10</v>
+        <v>10.83333333333333</v>
       </c>
       <c r="K11" t="n">
-        <v>-4.15</v>
+        <v>-4.91</v>
       </c>
       <c r="L11" t="n">
-        <v>5.26</v>
+        <v>5.46</v>
       </c>
       <c r="M11" t="n">
         <v>0.54</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,28 +1247,28 @@
         <v>3.66</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44917.55208333334</v>
+        <v>44918.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>17210</v>
+        <v>16950</v>
       </c>
       <c r="I12" t="n">
         <v>17088.33951186408</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K12" t="n">
-        <v>0.35</v>
+        <v>-1.17</v>
       </c>
       <c r="L12" t="n">
-        <v>0.91</v>
+        <v>2.03</v>
       </c>
       <c r="M12" t="n">
         <v>0.4</v>
       </c>
       <c r="N12" t="n">
-        <v>2.23</v>
+        <v>2.71</v>
       </c>
       <c r="O12" t="n">
         <v>0.53</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>4.79</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44959.55208333334</v>
+        <v>44960.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>17200</v>
+        <v>17292.5</v>
       </c>
       <c r="I13" t="n">
         <v>17272.92574993892</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>41.16666666666666</v>
+        <v>42</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.47</v>
+        <v>-2.02</v>
       </c>
       <c r="L13" t="n">
         <v>3.39</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>5.38</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>45026.38541666666</v>
+        <v>45026.55208333334</v>
       </c>
       <c r="H14" t="n">
-        <v>18749.95</v>
+        <v>18588.8</v>
       </c>
       <c r="I14" t="n">
         <v>18591.93662924636</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>66</v>
+        <v>66.16666666666667</v>
       </c>
       <c r="K14" t="n">
-        <v>8.43</v>
+        <v>7.5</v>
       </c>
       <c r="L14" t="n">
         <v>1.81</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>85</v>
+        <v>86</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -1275,28 +1454,28 @@
         <v>4.74</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>45043.55208333334</v>
+        <v>45044.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>19084.4</v>
+        <v>19370.25</v>
       </c>
       <c r="I15" t="n">
         <v>19288.7011099933</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>17</v>
+        <v>17.83333333333333</v>
       </c>
       <c r="K15" t="n">
-        <v>-2.67</v>
+        <v>-4.2</v>
       </c>
       <c r="L15" t="n">
-        <v>3.18</v>
+        <v>4.5</v>
       </c>
       <c r="M15" t="n">
         <v>0.53</v>
       </c>
       <c r="N15" t="n">
-        <v>1.02</v>
+        <v>1.5</v>
       </c>
       <c r="O15" t="n">
         <v>-1.47</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,28 +1523,28 @@
         <v>3.58</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>45057.55208333334</v>
+        <v>45058.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>19530</v>
+        <v>19035.8</v>
       </c>
       <c r="I16" t="n">
         <v>19104.16119477178</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K16" t="n">
-        <v>0.82</v>
+        <v>-1.73</v>
       </c>
       <c r="L16" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="M16" t="n">
         <v>0.6899999999999999</v>
       </c>
       <c r="N16" t="n">
-        <v>2.5</v>
+        <v>2.72</v>
       </c>
       <c r="O16" t="n">
         <v>1.5</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>6.21</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>45090.55208333334</v>
+        <v>45091.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>19060</v>
+        <v>19139.4</v>
       </c>
       <c r="I17" t="n">
         <v>19084.84738272116</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>32.16666666666666</v>
+        <v>33</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.13</v>
+        <v>-0.54</v>
       </c>
       <c r="L17" t="n">
         <v>3.12</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,22 +1661,22 @@
         <v>2.6</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>45100.38541666666</v>
+        <v>45100.55208333334</v>
       </c>
       <c r="H18" t="n">
-        <v>18709.05</v>
+        <v>18647.15</v>
       </c>
       <c r="I18" t="n">
         <v>18660.65298604292</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>9</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="K18" t="n">
-        <v>-2.25</v>
+        <v>-2.57</v>
       </c>
       <c r="L18" t="n">
-        <v>2.82</v>
+        <v>3.38</v>
       </c>
       <c r="M18" t="n">
         <v>0.1</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S18" t="b">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1503,25 +1730,25 @@
         <v>3.74</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45112.55208333334</v>
+        <v>45113.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>19200</v>
+        <v>19210.85</v>
       </c>
       <c r="I19" t="n">
         <v>19210.60151941694</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>12</v>
+        <v>12.83333333333333</v>
       </c>
       <c r="K19" t="n">
-        <v>-2.96</v>
+        <v>-3.02</v>
       </c>
       <c r="L19" t="n">
-        <v>3.39</v>
+        <v>4.14</v>
       </c>
       <c r="M19" t="n">
-        <v>0.3</v>
+        <v>0.49</v>
       </c>
       <c r="N19" t="n">
         <v>2.3</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,25 +1799,25 @@
         <v>3.29</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45120.55208333334</v>
+        <v>45121.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>19183.15</v>
+        <v>18815</v>
       </c>
       <c r="I20" t="n">
         <v>18970.32745947375</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.14</v>
+        <v>-2.06</v>
       </c>
       <c r="L20" t="n">
-        <v>0.87</v>
+        <v>2.45</v>
       </c>
       <c r="M20" t="n">
-        <v>0.08</v>
+        <v>0.7</v>
       </c>
       <c r="N20" t="n">
         <v>2.9</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S20" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>5.19</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45167.55208333334</v>
+        <v>45168.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>18625</v>
+        <v>18706.45</v>
       </c>
       <c r="I21" t="n">
         <v>18697.14872688635</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>46.16666666666666</v>
+        <v>47</v>
       </c>
       <c r="K21" t="n">
-        <v>1.01</v>
+        <v>0.58</v>
       </c>
       <c r="L21" t="n">
         <v>4.44</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>2.93</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45198.38541666666</v>
+        <v>45198.55208333334</v>
       </c>
       <c r="H22" t="n">
-        <v>19203.95</v>
+        <v>19015</v>
       </c>
       <c r="I22" t="n">
         <v>19032.81916155405</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>30</v>
+        <v>30.16666666666667</v>
       </c>
       <c r="K22" t="n">
-        <v>2.66</v>
+        <v>1.65</v>
       </c>
       <c r="L22" t="n">
         <v>1.08</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1731,22 +2006,22 @@
         <v>5.06</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45209.38541666666</v>
+        <v>45209.55208333334</v>
       </c>
       <c r="H23" t="n">
-        <v>19500</v>
+        <v>19710</v>
       </c>
       <c r="I23" t="n">
         <v>19553.34683988647</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>10.83333333333333</v>
+        <v>11</v>
       </c>
       <c r="K23" t="n">
-        <v>-2.55</v>
+        <v>-3.66</v>
       </c>
       <c r="L23" t="n">
-        <v>2.8</v>
+        <v>3.98</v>
       </c>
       <c r="M23" t="n">
         <v>0.32</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S23" t="b">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>4.11</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45222.55208333334</v>
+        <v>45224.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>19770</v>
+        <v>19626.7</v>
       </c>
       <c r="I24" t="n">
         <v>19753.24797577742</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>13</v>
+        <v>14.83333333333333</v>
       </c>
       <c r="K24" t="n">
-        <v>0.3</v>
+        <v>-0.42</v>
       </c>
       <c r="L24" t="n">
         <v>1.07</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1845,28 +2144,28 @@
         <v>5.82</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45245.55208333334</v>
+        <v>45246.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>19710</v>
+        <v>20609.4</v>
       </c>
       <c r="I25" t="n">
         <v>20149.44276876543</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.42</v>
+        <v>-5.01</v>
       </c>
       <c r="L25" t="n">
-        <v>2.59</v>
+        <v>5.36</v>
       </c>
       <c r="M25" t="n">
         <v>1.25</v>
       </c>
       <c r="N25" t="n">
-        <v>1.18</v>
+        <v>4.45</v>
       </c>
       <c r="O25" t="n">
         <v>-0.71</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>6.53</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45311.55208333334</v>
+        <v>45314.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>23030</v>
+        <v>22525.7</v>
       </c>
       <c r="I26" t="n">
         <v>22601.3225609586</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>65.16666666666667</v>
+        <v>68</v>
       </c>
       <c r="K26" t="n">
-        <v>11.75</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="L26" t="n">
         <v>4.55</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>92</v>
+        <v>93</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3</v>
+      </c>
+      <c r="U26" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="27">
@@ -1959,28 +2282,28 @@
         <v>5.35</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45320.55208333334</v>
+        <v>45321.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>23150</v>
+        <v>23991.95</v>
       </c>
       <c r="I27" t="n">
         <v>23470.11854492107</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K27" t="n">
-        <v>-2.77</v>
+        <v>-6.51</v>
       </c>
       <c r="L27" t="n">
-        <v>3.65</v>
+        <v>7.31</v>
       </c>
       <c r="M27" t="n">
         <v>0.58</v>
       </c>
       <c r="N27" t="n">
-        <v>1.76</v>
+        <v>3.24</v>
       </c>
       <c r="O27" t="n">
         <v>-1.22</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>6.43</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45364.38541666666</v>
+        <v>45364.55208333334</v>
       </c>
       <c r="H28" t="n">
-        <v>28713</v>
+        <v>28410.15</v>
       </c>
       <c r="I28" t="n">
         <v>28561.3720466193</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>43</v>
+        <v>43.16666666666666</v>
       </c>
       <c r="K28" t="n">
-        <v>19.68</v>
+        <v>18.42</v>
       </c>
       <c r="L28" t="n">
         <v>3.3</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,22 +2420,22 @@
         <v>6.5</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45372.55208333334</v>
+        <v>45373.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>29970</v>
+        <v>30412</v>
       </c>
       <c r="I29" t="n">
         <v>30258.10447091033</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>8</v>
+        <v>8.833333333333334</v>
       </c>
       <c r="K29" t="n">
-        <v>-5.49</v>
+        <v>-7.05</v>
       </c>
       <c r="L29" t="n">
-        <v>6.3</v>
+        <v>7.11</v>
       </c>
       <c r="M29" t="n">
         <v>0.39</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2130,22 +2489,22 @@
         <v>5.57</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45391.55208333334</v>
+        <v>45392.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>30128</v>
+        <v>29861.6</v>
       </c>
       <c r="I30" t="n">
         <v>29925.88701010625</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K30" t="n">
-        <v>-0.93</v>
+        <v>-1.81</v>
       </c>
       <c r="L30" t="n">
-        <v>2.24</v>
+        <v>3.41</v>
       </c>
       <c r="M30" t="n">
         <v>0.14</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,28 +2558,28 @@
         <v>5.06</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45412.55208333334</v>
+        <v>45414.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>29251</v>
+        <v>30616.85</v>
       </c>
       <c r="I31" t="n">
         <v>30262.64437172285</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K31" t="n">
-        <v>2.04</v>
+        <v>-2.53</v>
       </c>
       <c r="L31" t="n">
-        <v>1.97</v>
+        <v>2.82</v>
       </c>
       <c r="M31" t="n">
         <v>0.87</v>
       </c>
       <c r="N31" t="n">
-        <v>1.09</v>
+        <v>4.44</v>
       </c>
       <c r="O31" t="n">
         <v>-1.44</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,28 +2627,28 @@
         <v>7.33</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45446.55208333334</v>
+        <v>45447.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>30000</v>
+        <v>28715</v>
       </c>
       <c r="I32" t="n">
         <v>29866.17204867566</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>32.16666666666666</v>
+        <v>33</v>
       </c>
       <c r="K32" t="n">
-        <v>-2.01</v>
+        <v>-6.21</v>
       </c>
       <c r="L32" t="n">
-        <v>4.76</v>
+        <v>10.18</v>
       </c>
       <c r="M32" t="n">
         <v>0.61</v>
       </c>
       <c r="N32" t="n">
-        <v>3.28</v>
+        <v>3.33</v>
       </c>
       <c r="O32" t="n">
         <v>4.44</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,22 +2696,22 @@
         <v>9.369999999999999</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45455.55208333334</v>
+        <v>45456.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>31400</v>
+        <v>32141.4</v>
       </c>
       <c r="I33" t="n">
         <v>31406.21841939583</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K33" t="n">
-        <v>-9.35</v>
+        <v>-11.93</v>
       </c>
       <c r="L33" t="n">
-        <v>10.04</v>
+        <v>12.2</v>
       </c>
       <c r="M33" t="n">
         <v>2.58</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S33" t="b">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>6.72</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45506.55208333334</v>
+        <v>45509.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>33810</v>
+        <v>32447</v>
       </c>
       <c r="I34" t="n">
         <v>33686.92588709301</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>50.16666666666666</v>
+        <v>53</v>
       </c>
       <c r="K34" t="n">
-        <v>5.19</v>
+        <v>0.95</v>
       </c>
       <c r="L34" t="n">
         <v>2.15</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>3</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>7.07</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45530.38541666666</v>
+        <v>45530.55208333334</v>
       </c>
       <c r="H35" t="n">
-        <v>32563.45</v>
+        <v>32800</v>
       </c>
       <c r="I35" t="n">
         <v>32689.53772763136</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>21</v>
+        <v>21.16666666666667</v>
       </c>
       <c r="K35" t="n">
-        <v>-0.36</v>
+        <v>-1.09</v>
       </c>
       <c r="L35" t="n">
         <v>4.14</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S35" t="b">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>4.31</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45581.55208333334</v>
+        <v>45582.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>38160.5</v>
+        <v>36823.3</v>
       </c>
       <c r="I36" t="n">
         <v>36974.6360134268</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>51</v>
+        <v>51.83333333333334</v>
       </c>
       <c r="K36" t="n">
-        <v>16.34</v>
+        <v>12.27</v>
       </c>
       <c r="L36" t="n">
         <v>3.96</v>
@@ -2493,7 +2924,7 @@
         <v>1.12</v>
       </c>
       <c r="N36" t="n">
-        <v>3.61</v>
+        <v>4.32</v>
       </c>
       <c r="O36" t="n">
         <v>0.43</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>73</v>
+        <v>74</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>3</v>
+      </c>
+      <c r="U36" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>7.45</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45630.55208333334</v>
+        <v>45631.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>35240</v>
+        <v>36123.15</v>
       </c>
       <c r="I37" t="n">
         <v>35530.78741842067</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>48.16666666666666</v>
+        <v>49</v>
       </c>
       <c r="K37" t="n">
-        <v>4.3</v>
+        <v>1.9</v>
       </c>
       <c r="L37" t="n">
         <v>4.32</v>
@@ -2550,7 +2993,7 @@
         <v>1.83</v>
       </c>
       <c r="N37" t="n">
-        <v>2.47</v>
+        <v>3.01</v>
       </c>
       <c r="O37" t="n">
         <v>-4.32</v>
@@ -2559,7 +3002,19 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>3</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -2586,28 +3041,28 @@
         <v>5.63</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45645.55208333334</v>
+        <v>45646.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>35495</v>
+        <v>34790</v>
       </c>
       <c r="I38" t="n">
         <v>35226.25156461743</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K38" t="n">
-        <v>-1.74</v>
+        <v>-3.69</v>
       </c>
       <c r="L38" t="n">
-        <v>3.2</v>
+        <v>3.79</v>
       </c>
       <c r="M38" t="n">
         <v>0.42</v>
       </c>
       <c r="N38" t="n">
-        <v>2.03</v>
+        <v>2.73</v>
       </c>
       <c r="O38" t="n">
         <v>3.01</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>5.74</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45734.55208333334</v>
+        <v>45735.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>27385</v>
+        <v>27565.1</v>
       </c>
       <c r="I39" t="n">
         <v>27433.67060023599</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>88.16666666666667</v>
+        <v>89</v>
       </c>
       <c r="K39" t="n">
-        <v>21.28</v>
+        <v>20.77</v>
       </c>
       <c r="L39" t="n">
         <v>3.29</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>122</v>
+        <v>123</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>4</v>
+      </c>
+      <c r="U39" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="40">
@@ -2700,25 +3179,25 @@
         <v>4.65</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45751.55208333334</v>
+        <v>45754.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>27334</v>
+        <v>26356.15</v>
       </c>
       <c r="I40" t="n">
         <v>27102.76840834263</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K40" t="n">
-        <v>-0.84</v>
+        <v>-4.39</v>
       </c>
       <c r="L40" t="n">
-        <v>1.6</v>
+        <v>5.96</v>
       </c>
       <c r="M40" t="n">
-        <v>0.95</v>
+        <v>3.38</v>
       </c>
       <c r="N40" t="n">
         <v>3.07</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,22 +3248,22 @@
         <v>5.67</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45764.55208333334</v>
+        <v>45768.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>27490</v>
+        <v>27725</v>
       </c>
       <c r="I41" t="n">
         <v>27690.46659615497</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K41" t="n">
-        <v>-4.3</v>
+        <v>-5.19</v>
       </c>
       <c r="L41" t="n">
-        <v>4.64</v>
+        <v>5.97</v>
       </c>
       <c r="M41" t="n">
         <v>2.61</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>4.72</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45806.38541666666</v>
+        <v>45806.55208333334</v>
       </c>
       <c r="H42" t="n">
-        <v>31450</v>
+        <v>31250</v>
       </c>
       <c r="I42" t="n">
         <v>31265.84264300919</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>38</v>
+        <v>38.16666666666666</v>
       </c>
       <c r="K42" t="n">
-        <v>13.44</v>
+        <v>12.71</v>
       </c>
       <c r="L42" t="n">
         <v>0.76</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -2871,28 +3386,28 @@
         <v>4.78</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45821.55208333334</v>
+        <v>45824.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>31600</v>
+        <v>32295</v>
       </c>
       <c r="I43" t="n">
         <v>32292.8145533993</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>15</v>
+        <v>17.83333333333333</v>
       </c>
       <c r="K43" t="n">
-        <v>-1.12</v>
+        <v>-3.34</v>
       </c>
       <c r="L43" t="n">
-        <v>2.45</v>
+        <v>3.34</v>
       </c>
       <c r="M43" t="n">
         <v>1.12</v>
       </c>
       <c r="N43" t="n">
-        <v>1.27</v>
+        <v>2.18</v>
       </c>
       <c r="O43" t="n">
         <v>-1</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S43" t="b">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>5.17</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45874.55208333334</v>
+        <v>45875.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>40650</v>
+        <v>38570</v>
       </c>
       <c r="I44" t="n">
         <v>39156.18150147803</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>50.16666666666666</v>
+        <v>51</v>
       </c>
       <c r="K44" t="n">
-        <v>25.87</v>
+        <v>19.43</v>
       </c>
       <c r="L44" t="n">
         <v>2.76</v>
@@ -2949,7 +3476,7 @@
         <v>1.51</v>
       </c>
       <c r="N44" t="n">
-        <v>2.06</v>
+        <v>6.15</v>
       </c>
       <c r="O44" t="n">
         <v>2.18</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>74</v>
+        <v>75</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>3</v>
+      </c>
+      <c r="U44" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -2985,22 +3524,22 @@
         <v>9.359999999999999</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45898.55208333334</v>
+        <v>45901.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>39960</v>
+        <v>40650</v>
       </c>
       <c r="I45" t="n">
         <v>40292.64314021204</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>23.16666666666667</v>
+        <v>26</v>
       </c>
       <c r="K45" t="n">
-        <v>-3.6</v>
+        <v>-5.39</v>
       </c>
       <c r="L45" t="n">
-        <v>5.15</v>
+        <v>5.63</v>
       </c>
       <c r="M45" t="n">
         <v>1.33</v>
@@ -3015,7 +3554,19 @@
         <v>1</v>
       </c>
       <c r="Q45" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,22 +3593,22 @@
         <v>4.93</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45912.38541666666</v>
+        <v>45912.55208333334</v>
       </c>
       <c r="H46" t="n">
-        <v>40100</v>
+        <v>39880</v>
       </c>
       <c r="I46" t="n">
         <v>40058.9915469414</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>11</v>
+        <v>11.16666666666667</v>
       </c>
       <c r="K46" t="n">
-        <v>-1.35</v>
+        <v>-1.89</v>
       </c>
       <c r="L46" t="n">
-        <v>1.57</v>
+        <v>2.12</v>
       </c>
       <c r="M46" t="n">
         <v>0.06</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S46" t="b">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>3.99</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>46023.55208333334</v>
+        <v>46024.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>36170</v>
+        <v>39055</v>
       </c>
       <c r="I47" t="n">
         <v>36615.38485187612</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>111</v>
+        <v>111.8333333333333</v>
       </c>
       <c r="K47" t="n">
-        <v>9.300000000000001</v>
+        <v>2.07</v>
       </c>
       <c r="L47" t="n">
         <v>0.78</v>
@@ -3120,7 +3683,7 @@
         <v>1.17</v>
       </c>
       <c r="N47" t="n">
-        <v>1.52</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="O47" t="n">
         <v>-1.66</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>150</v>
+        <v>151</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>5</v>
+      </c>
+      <c r="U47" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>8.73</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>46031.55208333334</v>
+        <v>46034.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>37990</v>
+        <v>37230</v>
       </c>
       <c r="I48" t="n">
         <v>37303.10876304069</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>10</v>
       </c>
       <c r="K48" t="n">
-        <v>-2.73</v>
+        <v>-4.67</v>
       </c>
       <c r="L48" t="n">
         <v>7.44</v>
@@ -3186,7 +3761,19 @@
         <v>1</v>
       </c>
       <c r="Q48" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S48" t="b">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3213,28 +3800,28 @@
         <v>6.41</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>46055.55208333334</v>
+        <v>46056.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>36680</v>
+        <v>37625</v>
       </c>
       <c r="I49" t="n">
         <v>36916.56614465876</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K49" t="n">
-        <v>1.48</v>
+        <v>-1.06</v>
       </c>
       <c r="L49" t="n">
         <v>2.75</v>
       </c>
       <c r="M49" t="n">
-        <v>0.55</v>
+        <v>3.59</v>
       </c>
       <c r="N49" t="n">
-        <v>1.9</v>
+        <v>2.92</v>
       </c>
       <c r="O49" t="n">
         <v>-0.89</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,22 +3869,22 @@
         <v>5.57</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>46062.38541666666</v>
+        <v>46062.55208333334</v>
       </c>
       <c r="H50" t="n">
-        <v>36145</v>
+        <v>35670</v>
       </c>
       <c r="I50" t="n">
         <v>35750.4663606133</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>6</v>
+        <v>6.166666666666667</v>
       </c>
       <c r="K50" t="n">
-        <v>-3.93</v>
+        <v>-5.2</v>
       </c>
       <c r="L50" t="n">
-        <v>4.92</v>
+        <v>5.58</v>
       </c>
       <c r="M50" t="n">
         <v>0.13</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S50" t="b">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>6.43</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>46078.38541666666</v>
+        <v>46078.55208333334</v>
       </c>
       <c r="H51" t="n">
-        <v>36580</v>
+        <v>36660</v>
       </c>
       <c r="I51" t="n">
         <v>36595.52505695112</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>15.83333333333333</v>
+        <v>16</v>
       </c>
       <c r="K51" t="n">
-        <v>-2.55</v>
+        <v>-2.78</v>
       </c>
       <c r="L51" t="n">
         <v>5</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,28 +4007,28 @@
         <v>5.51</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>46083.55208333334</v>
+        <v>46085.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>35375</v>
+        <v>33685</v>
       </c>
       <c r="I52" t="n">
         <v>34807.36398412093</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>5</v>
+        <v>6.833333333333333</v>
       </c>
       <c r="K52" t="n">
-        <v>-3.51</v>
+        <v>-8.119999999999999</v>
       </c>
       <c r="L52" t="n">
-        <v>4.53</v>
+        <v>8.35</v>
       </c>
       <c r="M52" t="n">
         <v>1.5</v>
       </c>
       <c r="N52" t="n">
-        <v>2.82</v>
+        <v>5.75</v>
       </c>
       <c r="O52" t="n">
         <v>3.62</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S52" t="b">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3441,28 +4076,28 @@
         <v>8.42</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>46111.55208333334</v>
+        <v>46113.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>28750</v>
+        <v>30850</v>
       </c>
       <c r="I53" t="n">
         <v>30563.59893912671</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>26.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K53" t="n">
-        <v>14.65</v>
+        <v>8.42</v>
       </c>
       <c r="L53" t="n">
         <v>3.61</v>
       </c>
       <c r="M53" t="n">
-        <v>1.3</v>
+        <v>2.42</v>
       </c>
       <c r="N53" t="n">
-        <v>2.66</v>
+        <v>7.04</v>
       </c>
       <c r="O53" t="n">
         <v>-5.75</v>
@@ -3471,7 +4106,19 @@
         <v>1</v>
       </c>
       <c r="Q53" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>9.890000000000001</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>46141.55208333334</v>
+        <v>46142.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>36365</v>
+        <v>35885</v>
       </c>
       <c r="I54" t="n">
         <v>36319.53950284493</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>29</v>
       </c>
       <c r="K54" t="n">
-        <v>17.88</v>
+        <v>16.32</v>
       </c>
       <c r="L54" t="n">
         <v>5.61</v>
@@ -3528,7 +4175,19 @@
         <v>1</v>
       </c>
       <c r="Q54" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,28 +4214,28 @@
         <v>5.91</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>46148.55208333334</v>
+        <v>46149.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>36645</v>
+        <v>38225</v>
       </c>
       <c r="I55" t="n">
         <v>37710.06833290913</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K55" t="n">
-        <v>-2.12</v>
+        <v>-6.52</v>
       </c>
       <c r="L55" t="n">
-        <v>2.41</v>
+        <v>6.95</v>
       </c>
       <c r="M55" t="n">
-        <v>0.47</v>
+        <v>0.64</v>
       </c>
       <c r="N55" t="n">
-        <v>2.1</v>
+        <v>2.87</v>
       </c>
       <c r="O55" t="n">
         <v>-0.6</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S55" t="b">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>1</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -3612,28 +4283,28 @@
         <v>7.54</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46162.55208333334</v>
+        <v>46163.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>36715</v>
+        <v>35025</v>
       </c>
       <c r="I56" t="n">
         <v>36052.94589389826</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K56" t="n">
-        <v>-3.95</v>
+        <v>-8.369999999999999</v>
       </c>
       <c r="L56" t="n">
-        <v>5.65</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="M56" t="n">
         <v>0.5</v>
       </c>
       <c r="N56" t="n">
-        <v>2.05</v>
+        <v>4.32</v>
       </c>
       <c r="O56" t="n">
         <v>2.87</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S56" t="b">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -3669,22 +4352,22 @@
         <v>10.95</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46169.55208333334</v>
+        <v>46171.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>36025</v>
+        <v>37680</v>
       </c>
       <c r="I57" t="n">
         <v>37553.3051631256</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K57" t="n">
-        <v>-2.86</v>
+        <v>-7.58</v>
       </c>
       <c r="L57" t="n">
-        <v>7.35</v>
+        <v>8.35</v>
       </c>
       <c r="M57" t="n">
         <v>1.29</v>
@@ -3699,7 +4382,19 @@
         <v>1</v>
       </c>
       <c r="Q57" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,28 +4421,28 @@
         <v>7.77</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46266.55208333334</v>
+        <v>46267.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>48225</v>
+        <v>46665</v>
       </c>
       <c r="I58" t="n">
         <v>47148.10855893892</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>95.16666666666667</v>
+        <v>96</v>
       </c>
       <c r="K58" t="n">
-        <v>27.99</v>
+        <v>23.85</v>
       </c>
       <c r="L58" t="n">
         <v>5.11</v>
       </c>
       <c r="M58" t="n">
-        <v>0.82</v>
+        <v>0.92</v>
       </c>
       <c r="N58" t="n">
-        <v>2.03</v>
+        <v>2.17</v>
       </c>
       <c r="O58" t="n">
         <v>2.29</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>134</v>
+        <v>135</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>4</v>
+      </c>
+      <c r="U58" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="59">
@@ -3783,22 +4490,22 @@
         <v>5.97</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46272.55208333334</v>
+        <v>46273.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>48450</v>
+        <v>48785</v>
       </c>
       <c r="I59" t="n">
         <v>48709.60680083145</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K59" t="n">
-        <v>-3.83</v>
+        <v>-4.54</v>
       </c>
       <c r="L59" t="n">
-        <v>4.04</v>
+        <v>4.91</v>
       </c>
       <c r="M59" t="n">
         <v>0.41</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S59" t="b">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>1</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>5.03</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46293.38541666666</v>
+        <v>46293.55208333334</v>
       </c>
       <c r="H60" t="n">
-        <v>47040</v>
+        <v>47000</v>
       </c>
       <c r="I60" t="n">
         <v>47014.35878392406</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>20</v>
+        <v>20.16666666666667</v>
       </c>
       <c r="K60" t="n">
-        <v>-3.58</v>
+        <v>-3.66</v>
       </c>
       <c r="L60" t="n">
         <v>3.97</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S60" t="b">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -3897,25 +4628,25 @@
         <v>3.74</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46310.55208333334</v>
+        <v>46311.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>44600</v>
+        <v>45585</v>
       </c>
       <c r="I61" t="n">
         <v>45332.95583533429</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>17</v>
+        <v>17.83333333333333</v>
       </c>
       <c r="K61" t="n">
-        <v>5.11</v>
+        <v>3.01</v>
       </c>
       <c r="L61" t="n">
         <v>1.16</v>
       </c>
       <c r="M61" t="n">
-        <v>0.75</v>
+        <v>0.98</v>
       </c>
       <c r="N61" t="n">
         <v>2.42</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="62">
@@ -3978,6 +4721,14 @@
       <c r="Q62" t="n">
         <v>16</v>
       </c>
+      <c r="R62" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="inlineStr"/>
+      <c r="U62" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6080,7 +6831,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>27.8</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6">
@@ -6090,7 +6841,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20.1</v>
+        <v>20.6</v>
       </c>
     </row>
     <row r="7">
@@ -6100,7 +6851,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>111</v>
+        <v>111.8</v>
       </c>
     </row>
     <row r="8">
@@ -6110,7 +6861,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -6120,7 +6871,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>38.8</v>
+        <v>39.1</v>
       </c>
     </row>
     <row r="10">
@@ -6130,7 +6881,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>65.2</v>
+        <v>66.40000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -6140,7 +6891,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="12">
@@ -6150,7 +6901,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13">
@@ -6160,7 +6911,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>70</v>
+        <v>68.3</v>
       </c>
     </row>
     <row r="14">
@@ -6170,7 +6921,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.88</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="15">
@@ -6180,7 +6931,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.75</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="16">
@@ -6190,7 +6941,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>-1.21</v>
       </c>
     </row>
     <row r="17">
@@ -6200,7 +6951,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>27.99</v>
+        <v>23.85</v>
       </c>
     </row>
     <row r="18">
@@ -6210,7 +6961,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>45</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="19">
@@ -6220,7 +6971,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.38</v>
+        <v>4.19</v>
       </c>
     </row>
     <row r="20">
@@ -6230,7 +6981,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.15</v>
+        <v>3.87</v>
       </c>
     </row>
     <row r="21">
@@ -6240,7 +6991,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>10.04</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="22">
@@ -6250,7 +7001,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23">
@@ -6260,7 +7011,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -6270,7 +7021,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.02</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="25">
@@ -6280,7 +7031,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2.86</v>
+        <v>3.59</v>
       </c>
     </row>
     <row r="26">
@@ -6290,7 +7041,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.54</v>
+        <v>3.15</v>
       </c>
     </row>
     <row r="27">
@@ -6300,7 +7051,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>5.88</v>
+        <v>8.359999999999999</v>
       </c>
     </row>
     <row r="28">
@@ -6310,7 +7061,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="29">
